--- a/data/Field_Issues.xlsx
+++ b/data/Field_Issues.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F7C168-28E8-4AE5-A95A-11595FA4E49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issues" sheetId="1" r:id="rId1"/>
